--- a/data/result_20260911_115245 (additional acct linkage).xlsx
+++ b/data/result_20260911_115245 (additional acct linkage).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:28001_{D891EC35-20E9-489D-B483-0E18B1CA3258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38FB892-CA6A-4246-B3E8-4F9EEB576BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results export'!$A$1:$J$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$C$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$K$1:$O$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="20">
   <si>
     <t>target_user_id</t>
   </si>
@@ -97,12 +96,15 @@
   <si>
     <t>Count</t>
   </si>
+  <si>
+    <t>unique_user_id</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -117,6 +119,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -126,12 +134,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -141,8 +164,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,6 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -574,11 +598,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>8200826</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>36425882</v>
       </c>
       <c r="C2" t="s">
@@ -606,11 +630,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>8200826</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>36425882</v>
       </c>
       <c r="C3" t="s">
@@ -639,10 +663,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4">
+        <v>42406507</v>
+      </c>
+      <c r="B4">
         <v>2542992</v>
       </c>
       <c r="C4" t="s">
@@ -671,10 +695,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="A5">
+        <v>42406507</v>
+      </c>
+      <c r="B5">
         <v>3158809</v>
       </c>
       <c r="C5" t="s">
@@ -703,10 +727,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6">
+        <v>42406507</v>
+      </c>
+      <c r="B6">
         <v>3281810</v>
       </c>
       <c r="C6" t="s">
@@ -735,10 +759,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="A7">
+        <v>42406507</v>
+      </c>
+      <c r="B7">
         <v>3415189</v>
       </c>
       <c r="C7" t="s">
@@ -767,10 +791,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="A8">
+        <v>42406507</v>
+      </c>
+      <c r="B8">
         <v>3434386</v>
       </c>
       <c r="C8" t="s">
@@ -799,10 +823,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B9" s="1">
+      <c r="A9">
+        <v>42406507</v>
+      </c>
+      <c r="B9">
         <v>3531594</v>
       </c>
       <c r="C9" t="s">
@@ -831,10 +855,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B10" s="1">
+      <c r="A10">
+        <v>42406507</v>
+      </c>
+      <c r="B10">
         <v>3819032</v>
       </c>
       <c r="C10" t="s">
@@ -863,10 +887,10 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B11" s="1">
+      <c r="A11">
+        <v>42406507</v>
+      </c>
+      <c r="B11">
         <v>4167618</v>
       </c>
       <c r="C11" t="s">
@@ -895,10 +919,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B12" s="1">
+      <c r="A12">
+        <v>42406507</v>
+      </c>
+      <c r="B12">
         <v>4179701</v>
       </c>
       <c r="C12" t="s">
@@ -927,10 +951,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B13" s="1">
+      <c r="A13">
+        <v>42406507</v>
+      </c>
+      <c r="B13">
         <v>4188518</v>
       </c>
       <c r="C13" t="s">
@@ -959,10 +983,10 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="A14">
+        <v>42406507</v>
+      </c>
+      <c r="B14">
         <v>4253659</v>
       </c>
       <c r="C14" t="s">
@@ -991,10 +1015,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B15" s="1">
+      <c r="A15">
+        <v>42406507</v>
+      </c>
+      <c r="B15">
         <v>4276951</v>
       </c>
       <c r="C15" t="s">
@@ -1023,10 +1047,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B16" s="1">
+      <c r="A16">
+        <v>42406507</v>
+      </c>
+      <c r="B16">
         <v>4726514</v>
       </c>
       <c r="C16" t="s">
@@ -1055,10 +1079,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B17" s="1">
+      <c r="A17">
+        <v>42406507</v>
+      </c>
+      <c r="B17">
         <v>42011766</v>
       </c>
       <c r="C17" t="s">
@@ -1087,10 +1111,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B18" s="1">
+      <c r="A18">
+        <v>42406507</v>
+      </c>
+      <c r="B18">
         <v>42011766</v>
       </c>
       <c r="C18" t="s">
@@ -1119,10 +1143,10 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="A19">
+        <v>42406507</v>
+      </c>
+      <c r="B19">
         <v>42011817</v>
       </c>
       <c r="C19" t="s">
@@ -1151,10 +1175,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B20" s="1">
+      <c r="A20">
+        <v>42406507</v>
+      </c>
+      <c r="B20">
         <v>42012426</v>
       </c>
       <c r="C20" t="s">
@@ -1183,10 +1207,10 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="A21">
+        <v>42406507</v>
+      </c>
+      <c r="B21">
         <v>42077631</v>
       </c>
       <c r="C21" t="s">
@@ -1215,10 +1239,10 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="A22">
+        <v>42406507</v>
+      </c>
+      <c r="B22">
         <v>42426592</v>
       </c>
       <c r="C22" t="s">
@@ -1247,10 +1271,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="A23">
+        <v>42406507</v>
+      </c>
+      <c r="B23">
         <v>42426592</v>
       </c>
       <c r="C23" t="s">
@@ -1279,10 +1303,10 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="A24">
+        <v>42406507</v>
+      </c>
+      <c r="B24">
         <v>42426641</v>
       </c>
       <c r="C24" t="s">
@@ -1311,10 +1335,10 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B25" s="1">
+      <c r="A25">
+        <v>42406507</v>
+      </c>
+      <c r="B25">
         <v>42426641</v>
       </c>
       <c r="C25" t="s">
@@ -1343,10 +1367,10 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B26" s="1">
+      <c r="A26">
+        <v>42406507</v>
+      </c>
+      <c r="B26">
         <v>42758642</v>
       </c>
       <c r="C26" t="s">
@@ -1375,10 +1399,10 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B27" s="1">
+      <c r="A27">
+        <v>42406507</v>
+      </c>
+      <c r="B27">
         <v>42787717</v>
       </c>
       <c r="C27" t="s">
@@ -1407,10 +1431,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B28" s="1">
+      <c r="A28">
+        <v>42406507</v>
+      </c>
+      <c r="B28">
         <v>42787717</v>
       </c>
       <c r="C28" t="s">
@@ -1438,11 +1462,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>42426592</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29">
         <v>42011766</v>
       </c>
       <c r="C29" t="s">
@@ -1470,11 +1494,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>42426592</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30">
         <v>42406507</v>
       </c>
       <c r="C30" t="s">
@@ -1502,11 +1526,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>42426592</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31">
         <v>42406507</v>
       </c>
       <c r="C31" t="s">
@@ -1534,11 +1558,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>42426592</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>42426641</v>
       </c>
       <c r="C32" t="s">
@@ -1566,11 +1590,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>42426592</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33">
         <v>42426641</v>
       </c>
       <c r="C33" t="s">
@@ -1598,11 +1622,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>42426592</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34">
         <v>42787717</v>
       </c>
       <c r="C34" t="s">
@@ -1630,11 +1654,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>42426641</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35">
         <v>42406507</v>
       </c>
       <c r="C35" t="s">
@@ -1662,11 +1686,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>42426641</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36">
         <v>42406507</v>
       </c>
       <c r="C36" t="s">
@@ -1694,11 +1718,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>42426641</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37">
         <v>42426592</v>
       </c>
       <c r="C37" t="s">
@@ -1726,11 +1750,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>42426641</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38">
         <v>42426592</v>
       </c>
       <c r="C38" t="s">
@@ -1758,11 +1782,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>42426641</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39">
         <v>42598944</v>
       </c>
       <c r="C39" t="s">
@@ -1790,11 +1814,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>42458992</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40">
         <v>42459099</v>
       </c>
       <c r="C40" t="s">
@@ -1822,11 +1846,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>42458992</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41">
         <v>42459099</v>
       </c>
       <c r="C41" t="s">
@@ -1854,11 +1878,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>42458992</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42">
         <v>42459206</v>
       </c>
       <c r="C42" t="s">
@@ -1886,11 +1910,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>42458992</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43">
         <v>42459206</v>
       </c>
       <c r="C43" t="s">
@@ -1918,11 +1942,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>42458992</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44">
         <v>42459241</v>
       </c>
       <c r="C44" t="s">
@@ -1950,11 +1974,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>42458992</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45">
         <v>42459241</v>
       </c>
       <c r="C45" t="s">
@@ -1982,11 +2006,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>42458992</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46">
         <v>42459298</v>
       </c>
       <c r="C46" t="s">
@@ -2014,11 +2038,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>42458992</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47">
         <v>42459298</v>
       </c>
       <c r="C47" t="s">
@@ -2046,11 +2070,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>42459041</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48">
         <v>42458992</v>
       </c>
       <c r="C48" t="s">
@@ -2078,11 +2102,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>42459041</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49">
         <v>42458992</v>
       </c>
       <c r="C49" t="s">
@@ -2110,11 +2134,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>42459041</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50">
         <v>42459099</v>
       </c>
       <c r="C50" t="s">
@@ -2142,11 +2166,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>42459041</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51">
         <v>42459099</v>
       </c>
       <c r="C51" t="s">
@@ -2174,11 +2198,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>42459041</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52">
         <v>42459148</v>
       </c>
       <c r="C52" t="s">
@@ -2206,11 +2230,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>42459041</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53">
         <v>42459148</v>
       </c>
       <c r="C53" t="s">
@@ -2238,11 +2262,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54">
         <v>42459041</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54">
         <v>42459206</v>
       </c>
       <c r="C54" t="s">
@@ -2270,11 +2294,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>42459041</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55">
         <v>42459206</v>
       </c>
       <c r="C55" t="s">
@@ -2302,11 +2326,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56">
         <v>42459099</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56">
         <v>42458992</v>
       </c>
       <c r="C56" t="s">
@@ -2334,11 +2358,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57">
         <v>42459099</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57">
         <v>42458992</v>
       </c>
       <c r="C57" t="s">
@@ -2366,11 +2390,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58">
         <v>42459099</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58">
         <v>42459148</v>
       </c>
       <c r="C58" t="s">
@@ -2398,11 +2422,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>42459099</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59">
         <v>42459148</v>
       </c>
       <c r="C59" t="s">
@@ -2430,11 +2454,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>42459099</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60">
         <v>42459206</v>
       </c>
       <c r="C60" t="s">
@@ -2462,11 +2486,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>42459099</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>42459206</v>
       </c>
       <c r="C61" t="s">
@@ -2494,11 +2518,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>42459241</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>42458992</v>
       </c>
       <c r="C62" t="s">
@@ -2526,11 +2550,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63">
         <v>42459241</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>42458992</v>
       </c>
       <c r="C63" t="s">
@@ -2558,11 +2582,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64">
         <v>42459241</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>42459099</v>
       </c>
       <c r="C64" t="s">
@@ -2590,11 +2614,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>42459241</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>42459099</v>
       </c>
       <c r="C65" t="s">
@@ -2622,11 +2646,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66">
         <v>42459298</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>42459099</v>
       </c>
       <c r="C66" t="s">
@@ -2654,11 +2678,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67">
         <v>42459298</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>42459099</v>
       </c>
       <c r="C67" t="s">
@@ -2686,11 +2710,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>42459298</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>42459148</v>
       </c>
       <c r="C68" t="s">
@@ -2718,11 +2742,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A69">
         <v>42459298</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>42459148</v>
       </c>
       <c r="C69" t="s">
@@ -2750,11 +2774,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70">
         <v>42459298</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>42459206</v>
       </c>
       <c r="C70" t="s">
@@ -2782,11 +2806,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71">
         <v>42459298</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>42459206</v>
       </c>
       <c r="C71" t="s">
@@ -2814,11 +2838,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A72">
         <v>42705635</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72">
         <v>42758642</v>
       </c>
       <c r="C72" t="s">
@@ -2846,11 +2870,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73">
         <v>42731028</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73">
         <v>42705635</v>
       </c>
       <c r="C73" t="s">
@@ -2878,11 +2902,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74">
         <v>42731028</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74">
         <v>42705635</v>
       </c>
       <c r="C74" t="s">
@@ -2910,11 +2934,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75">
         <v>42731028</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75">
         <v>42787717</v>
       </c>
       <c r="C75" t="s">
@@ -2942,11 +2966,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A76">
         <v>42997602</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76">
         <v>43022302</v>
       </c>
       <c r="C76" t="s">
@@ -2974,11 +2998,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77">
         <v>42997602</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77">
         <v>43022302</v>
       </c>
       <c r="C77" t="s">
@@ -3006,11 +3030,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78">
         <v>42997602</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78">
         <v>43022440</v>
       </c>
       <c r="C78" t="s">
@@ -3038,11 +3062,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A79">
         <v>42997602</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79">
         <v>43022440</v>
       </c>
       <c r="C79" t="s">
@@ -3070,11 +3094,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A80">
         <v>43346700</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>43375656</v>
       </c>
       <c r="C80" t="s">
@@ -3102,11 +3126,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81">
         <v>43346700</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81">
         <v>43375656</v>
       </c>
       <c r="C81" t="s">
@@ -3134,11 +3158,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82">
         <v>8200826</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82">
         <v>16372934</v>
       </c>
       <c r="C82" t="s">
@@ -3166,11 +3190,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83">
         <v>8200826</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83">
         <v>16372934</v>
       </c>
       <c r="C83" t="s">
@@ -3199,10 +3223,10 @@
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B84" s="1">
+      <c r="A84">
+        <v>42406507</v>
+      </c>
+      <c r="B84">
         <v>3463245</v>
       </c>
       <c r="C84" t="s">
@@ -3231,10 +3255,10 @@
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B85" s="1">
+      <c r="A85">
+        <v>42406507</v>
+      </c>
+      <c r="B85">
         <v>3711577</v>
       </c>
       <c r="C85" t="s">
@@ -3263,10 +3287,10 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B86" s="1">
+      <c r="A86">
+        <v>42406507</v>
+      </c>
+      <c r="B86">
         <v>3728922</v>
       </c>
       <c r="C86" t="s">
@@ -3295,10 +3319,10 @@
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B87" s="1">
+      <c r="A87">
+        <v>42406507</v>
+      </c>
+      <c r="B87">
         <v>3754003</v>
       </c>
       <c r="C87" t="s">
@@ -3327,10 +3351,10 @@
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B88" s="1">
+      <c r="A88">
+        <v>42406507</v>
+      </c>
+      <c r="B88">
         <v>4239307</v>
       </c>
       <c r="C88" t="s">
@@ -3359,10 +3383,10 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B89" s="1">
+      <c r="A89">
+        <v>42406507</v>
+      </c>
+      <c r="B89">
         <v>31956677</v>
       </c>
       <c r="C89" t="s">
@@ -3391,10 +3415,10 @@
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B90" s="1">
+      <c r="A90">
+        <v>42406507</v>
+      </c>
+      <c r="B90">
         <v>42010347</v>
       </c>
       <c r="C90" t="s">
@@ -3423,10 +3447,10 @@
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B91" s="1">
+      <c r="A91">
+        <v>42406507</v>
+      </c>
+      <c r="B91">
         <v>42012522</v>
       </c>
       <c r="C91" t="s">
@@ -3455,10 +3479,10 @@
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B92" s="1">
+      <c r="A92">
+        <v>42406507</v>
+      </c>
+      <c r="B92">
         <v>42079879</v>
       </c>
       <c r="C92" t="s">
@@ -3487,10 +3511,10 @@
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B93" s="1">
+      <c r="A93">
+        <v>42406507</v>
+      </c>
+      <c r="B93">
         <v>42598944</v>
       </c>
       <c r="C93" t="s">
@@ -3519,10 +3543,10 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B94" s="1">
+      <c r="A94">
+        <v>42406507</v>
+      </c>
+      <c r="B94">
         <v>42598944</v>
       </c>
       <c r="C94" t="s">
@@ -3551,10 +3575,10 @@
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B95" s="1">
+      <c r="A95">
+        <v>42406507</v>
+      </c>
+      <c r="B95">
         <v>42814075</v>
       </c>
       <c r="C95" t="s">
@@ -3583,10 +3607,10 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B96" s="1">
+      <c r="A96">
+        <v>42406507</v>
+      </c>
+      <c r="B96">
         <v>42814075</v>
       </c>
       <c r="C96" t="s">
@@ -3615,10 +3639,10 @@
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B97" s="1">
+      <c r="A97">
+        <v>42406507</v>
+      </c>
+      <c r="B97">
         <v>43110281</v>
       </c>
       <c r="C97" t="s">
@@ -3647,10 +3671,10 @@
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B98" s="1">
+      <c r="A98">
+        <v>42406507</v>
+      </c>
+      <c r="B98">
         <v>43110281</v>
       </c>
       <c r="C98" t="s">
@@ -3678,11 +3702,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99">
         <v>42426592</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99">
         <v>42598944</v>
       </c>
       <c r="C99" t="s">
@@ -3710,11 +3734,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100">
         <v>42426592</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100">
         <v>42814075</v>
       </c>
       <c r="C100" t="s">
@@ -3742,11 +3766,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101">
         <v>42426592</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101">
         <v>43110281</v>
       </c>
       <c r="C101" t="s">
@@ -3774,11 +3798,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102">
         <v>42426641</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102">
         <v>42011766</v>
       </c>
       <c r="C102" t="s">
@@ -3806,11 +3830,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103">
         <v>42426641</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103">
         <v>42787717</v>
       </c>
       <c r="C103" t="s">
@@ -3838,11 +3862,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104">
         <v>42426641</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104">
         <v>42814075</v>
       </c>
       <c r="C104" t="s">
@@ -3870,11 +3894,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105">
         <v>42426641</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105">
         <v>43110281</v>
       </c>
       <c r="C105" t="s">
@@ -3902,11 +3926,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106">
         <v>42458992</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106">
         <v>42459041</v>
       </c>
       <c r="C106" t="s">
@@ -3934,11 +3958,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107">
         <v>42458992</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107">
         <v>42459041</v>
       </c>
       <c r="C107" t="s">
@@ -3966,11 +3990,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108">
         <v>42458992</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108">
         <v>42459148</v>
       </c>
       <c r="C108" t="s">
@@ -3998,11 +4022,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A109">
         <v>42458992</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109">
         <v>42459148</v>
       </c>
       <c r="C109" t="s">
@@ -4030,11 +4054,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110">
         <v>42459041</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110">
         <v>42459241</v>
       </c>
       <c r="C110" t="s">
@@ -4062,11 +4086,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111">
         <v>42459041</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111">
         <v>42459241</v>
       </c>
       <c r="C111" t="s">
@@ -4094,11 +4118,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A112">
         <v>42459041</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112">
         <v>42459298</v>
       </c>
       <c r="C112" t="s">
@@ -4126,11 +4150,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113">
         <v>42459041</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113">
         <v>42459298</v>
       </c>
       <c r="C113" t="s">
@@ -4158,11 +4182,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114">
         <v>42459099</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114">
         <v>42459041</v>
       </c>
       <c r="C114" t="s">
@@ -4190,11 +4214,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A115">
         <v>42459099</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115">
         <v>42459041</v>
       </c>
       <c r="C115" t="s">
@@ -4222,11 +4246,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116">
         <v>42459099</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116">
         <v>42459241</v>
       </c>
       <c r="C116" t="s">
@@ -4254,11 +4278,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117">
         <v>42459099</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117">
         <v>42459241</v>
       </c>
       <c r="C117" t="s">
@@ -4286,11 +4310,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118">
         <v>42459099</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118">
         <v>42459298</v>
       </c>
       <c r="C118" t="s">
@@ -4318,11 +4342,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119">
         <v>42459099</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119">
         <v>42459298</v>
       </c>
       <c r="C119" t="s">
@@ -4350,11 +4374,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120">
         <v>42459241</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120">
         <v>42459041</v>
       </c>
       <c r="C120" t="s">
@@ -4382,11 +4406,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121">
         <v>42459241</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121">
         <v>42459041</v>
       </c>
       <c r="C121" t="s">
@@ -4414,11 +4438,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122">
         <v>42459241</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122">
         <v>42459148</v>
       </c>
       <c r="C122" t="s">
@@ -4446,11 +4470,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A123" s="1">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123">
         <v>42459241</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123">
         <v>42459148</v>
       </c>
       <c r="C123" t="s">
@@ -4478,11 +4502,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124">
         <v>42459241</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124">
         <v>42459206</v>
       </c>
       <c r="C124" t="s">
@@ -4510,11 +4534,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125">
         <v>42459241</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125">
         <v>42459206</v>
       </c>
       <c r="C125" t="s">
@@ -4542,11 +4566,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126">
         <v>42459241</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126">
         <v>42459298</v>
       </c>
       <c r="C126" t="s">
@@ -4574,11 +4598,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127">
         <v>42459241</v>
       </c>
-      <c r="B127" s="1">
+      <c r="B127">
         <v>42459298</v>
       </c>
       <c r="C127" t="s">
@@ -4606,11 +4630,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128">
         <v>42459298</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128">
         <v>42458992</v>
       </c>
       <c r="C128" t="s">
@@ -4638,11 +4662,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129">
         <v>42459298</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129">
         <v>42458992</v>
       </c>
       <c r="C129" t="s">
@@ -4670,11 +4694,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130">
         <v>42459298</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130">
         <v>42459041</v>
       </c>
       <c r="C130" t="s">
@@ -4702,11 +4726,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131">
         <v>42459298</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131">
         <v>42459041</v>
       </c>
       <c r="C131" t="s">
@@ -4734,11 +4758,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132">
         <v>42459298</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B132">
         <v>42459241</v>
       </c>
       <c r="C132" t="s">
@@ -4766,11 +4790,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133">
         <v>42459298</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133">
         <v>42459241</v>
       </c>
       <c r="C133" t="s">
@@ -4798,11 +4822,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134">
         <v>42463024</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134">
         <v>42463063</v>
       </c>
       <c r="C134" t="s">
@@ -4830,11 +4854,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135">
         <v>42463024</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135">
         <v>42463063</v>
       </c>
       <c r="C135" t="s">
@@ -4862,11 +4886,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A136">
         <v>42463063</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136">
         <v>42463024</v>
       </c>
       <c r="C136" t="s">
@@ -4894,11 +4918,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A137">
         <v>42463063</v>
       </c>
-      <c r="B137" s="1">
+      <c r="B137">
         <v>42463024</v>
       </c>
       <c r="C137" t="s">
@@ -4926,11 +4950,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A138">
         <v>42705635</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B138">
         <v>42731028</v>
       </c>
       <c r="C138" t="s">
@@ -4958,11 +4982,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A139">
         <v>42705635</v>
       </c>
-      <c r="B139" s="1">
+      <c r="B139">
         <v>42731028</v>
       </c>
       <c r="C139" t="s">
@@ -4990,11 +5014,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140">
         <v>42731028</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140">
         <v>42758642</v>
       </c>
       <c r="C140" t="s">
@@ -5022,11 +5046,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A141">
         <v>42731028</v>
       </c>
-      <c r="B141" s="1">
+      <c r="B141">
         <v>42758642</v>
       </c>
       <c r="C141" t="s">
@@ -5054,11 +5078,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A142" s="1">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A142">
         <v>43593087</v>
       </c>
-      <c r="B142" s="1">
+      <c r="B142">
         <v>43613297</v>
       </c>
       <c r="C142" t="s">
@@ -5086,11 +5110,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A143">
         <v>43593087</v>
       </c>
-      <c r="B143" s="1">
+      <c r="B143">
         <v>43613297</v>
       </c>
       <c r="C143" t="s">
@@ -5119,7 +5143,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J143" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J143" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="42406507"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5127,619 +5157,1183 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25ED12FD-7613-4161-AB77-60A5E5F0FD4C}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>8200826</v>
+      </c>
+      <c r="B2">
         <v>36425882</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2">
+        <v>8200826</v>
+      </c>
+      <c r="L2">
+        <v>36425882</v>
+      </c>
+      <c r="M2" s="2"/>
+      <c r="O2">
+        <v>8200826</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>42406507</v>
+      </c>
+      <c r="B3">
         <v>2542992</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="K3">
+        <v>42406507</v>
+      </c>
+      <c r="L3">
+        <v>2542992</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="O3">
+        <v>42406507</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>42406507</v>
+      </c>
+      <c r="B4">
         <v>3158809</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="K4">
+        <v>42406507</v>
+      </c>
+      <c r="L4">
+        <v>3158809</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="O4">
+        <v>42426592</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>42406507</v>
+      </c>
+      <c r="B5">
         <v>3281810</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <f>COUNTA(C2:C52)</f>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <f>COUNTA(D2:D52)</f>
         <v>51</v>
       </c>
-      <c r="F5">
-        <f>COUNTIF(C2:C52,F4)</f>
+      <c r="G5">
+        <f>COUNTIF(D2:D52,G4)</f>
         <v>29</v>
       </c>
-      <c r="G5">
-        <f>COUNTIF(C2:C52,G4)</f>
+      <c r="H5">
+        <f>COUNTIF(D2:D52,H4)</f>
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="K5">
+        <v>42406507</v>
+      </c>
+      <c r="L5">
+        <v>3281810</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="O5">
+        <v>42426641</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>42406507</v>
+      </c>
+      <c r="B6">
         <v>3415189</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2">
-        <f>F5/E5</f>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1">
+        <f>G5/F5</f>
         <v>0.56862745098039214</v>
       </c>
-      <c r="G6" s="2">
-        <f>G5/E5</f>
+      <c r="H6" s="1">
+        <f>H5/F5</f>
         <v>0.43137254901960786</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="K6">
+        <v>42406507</v>
+      </c>
+      <c r="L6">
+        <v>3415189</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="O6">
+        <v>42458992</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>42406507</v>
+      </c>
+      <c r="B7">
         <v>3434386</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>42406507</v>
+      </c>
+      <c r="L7">
+        <v>3434386</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="O7">
+        <v>42459041</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>42406507</v>
+      </c>
+      <c r="B8">
         <v>3531594</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8">
+        <v>42406507</v>
+      </c>
+      <c r="L8">
+        <v>3531594</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="O8">
+        <v>42731028</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>42406507</v>
+      </c>
+      <c r="B9">
         <v>3819032</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9">
+        <v>42406507</v>
+      </c>
+      <c r="L9">
+        <v>3819032</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="O9">
+        <v>42997602</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>42406507</v>
+      </c>
+      <c r="B10">
         <v>4167618</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="K10">
+        <v>42406507</v>
+      </c>
+      <c r="L10">
+        <v>4167618</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="O10">
+        <v>43346700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>42406507</v>
+      </c>
+      <c r="B11">
         <v>4179701</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11">
+        <v>42406507</v>
+      </c>
+      <c r="L11">
+        <v>4179701</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="O11">
+        <v>42463024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>42406507</v>
+      </c>
+      <c r="B12">
         <v>4188518</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="K12">
+        <v>42406507</v>
+      </c>
+      <c r="L12">
+        <v>4188518</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="O12">
+        <v>42463063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>42406507</v>
+      </c>
+      <c r="B13">
         <v>4253659</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="K13">
+        <v>42406507</v>
+      </c>
+      <c r="L13">
+        <v>4253659</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="O13">
+        <v>42705635</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>42406507</v>
+      </c>
+      <c r="B14">
         <v>4276951</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14">
+        <v>42406507</v>
+      </c>
+      <c r="L14">
+        <v>4276951</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="O14">
+        <v>43593087</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>42406507</v>
+      </c>
+      <c r="B15">
         <v>4726514</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15">
+        <v>42406507</v>
+      </c>
+      <c r="L15">
+        <v>4726514</v>
+      </c>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>42406507</v>
+      </c>
+      <c r="B16">
         <v>42011766</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16">
+        <v>42406507</v>
+      </c>
+      <c r="L16">
+        <v>42011766</v>
+      </c>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>42406507</v>
+      </c>
+      <c r="B17">
         <v>42011817</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17">
+        <v>42406507</v>
+      </c>
+      <c r="L17">
+        <v>42011817</v>
+      </c>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>42406507</v>
+      </c>
+      <c r="B18">
         <v>42012426</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18">
+        <v>42406507</v>
+      </c>
+      <c r="L18">
+        <v>42012426</v>
+      </c>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>42406507</v>
+      </c>
+      <c r="B19">
         <v>42077631</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19">
+        <v>42406507</v>
+      </c>
+      <c r="L19">
+        <v>42077631</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>42406507</v>
+      </c>
+      <c r="B20">
         <v>42426592</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="K20">
+        <v>42406507</v>
+      </c>
+      <c r="L20">
+        <v>42426592</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>42406507</v>
+      </c>
+      <c r="B21">
         <v>42426641</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="K21">
+        <v>42406507</v>
+      </c>
+      <c r="L21">
+        <v>42426641</v>
+      </c>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>42406507</v>
+      </c>
+      <c r="B22">
         <v>42758642</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="K22">
+        <v>42406507</v>
+      </c>
+      <c r="L22">
+        <v>42758642</v>
+      </c>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>42406507</v>
+      </c>
+      <c r="B23">
         <v>42787717</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>10</v>
+      <c r="K23">
+        <v>42406507</v>
+      </c>
+      <c r="L23">
+        <v>42787717</v>
+      </c>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>42426592</v>
+      </c>
+      <c r="B24">
+        <v>42406507</v>
       </c>
       <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="K24">
+        <v>42426592</v>
+      </c>
+      <c r="L24">
+        <v>42406507</v>
+      </c>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>42426641</v>
+      </c>
+      <c r="B25">
         <v>42598944</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="K25">
+        <v>42426641</v>
+      </c>
+      <c r="L25">
+        <v>42598944</v>
+      </c>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>42458992</v>
+      </c>
+      <c r="B26">
         <v>42459099</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="K26">
+        <v>42458992</v>
+      </c>
+      <c r="L26">
+        <v>42459099</v>
+      </c>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>42458992</v>
+      </c>
+      <c r="B27">
         <v>42459206</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="K27">
+        <v>42458992</v>
+      </c>
+      <c r="L27">
+        <v>42459206</v>
+      </c>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>42458992</v>
+      </c>
+      <c r="B28">
         <v>42459241</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="K28">
+        <v>42458992</v>
+      </c>
+      <c r="L28">
+        <v>42459241</v>
+      </c>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>42458992</v>
+      </c>
+      <c r="B29">
         <v>42459298</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29">
         <v>42458992</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>10</v>
+      <c r="L29">
+        <v>42459298</v>
+      </c>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>42459041</v>
+      </c>
+      <c r="B30">
+        <v>42458992</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30">
+        <v>42459041</v>
+      </c>
+      <c r="L30">
+        <v>42458992</v>
+      </c>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>42459041</v>
+      </c>
+      <c r="B31">
         <v>42459148</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="K31">
+        <v>42459041</v>
+      </c>
+      <c r="L31">
+        <v>42459148</v>
+      </c>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>42731028</v>
+      </c>
+      <c r="B32">
         <v>42705635</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="K32">
+        <v>42731028</v>
+      </c>
+      <c r="L32">
+        <v>42705635</v>
+      </c>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>42997602</v>
+      </c>
+      <c r="B33">
         <v>43022302</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33">
+        <v>42997602</v>
+      </c>
+      <c r="L33">
+        <v>43022302</v>
+      </c>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>42997602</v>
+      </c>
+      <c r="B34">
         <v>43022440</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34">
+        <v>42997602</v>
+      </c>
+      <c r="L34">
+        <v>43022440</v>
+      </c>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>43346700</v>
+      </c>
+      <c r="B35">
         <v>43375656</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35">
+        <v>43346700</v>
+      </c>
+      <c r="L35">
+        <v>43375656</v>
+      </c>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>8200826</v>
+      </c>
+      <c r="B36">
         <v>16372934</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36">
+        <v>8200826</v>
+      </c>
+      <c r="L36">
+        <v>16372934</v>
+      </c>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>42406507</v>
+      </c>
+      <c r="B37">
         <v>3463245</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="C37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37">
+        <v>42406507</v>
+      </c>
+      <c r="L37">
+        <v>3463245</v>
+      </c>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>42406507</v>
+      </c>
+      <c r="B38">
         <v>3711577</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38">
+        <v>42406507</v>
+      </c>
+      <c r="L38">
+        <v>3711577</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>42406507</v>
+      </c>
+      <c r="B39">
         <v>3728922</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="C39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39">
+        <v>42406507</v>
+      </c>
+      <c r="L39">
+        <v>3728922</v>
+      </c>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>42406507</v>
+      </c>
+      <c r="B40">
         <v>3754003</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="C40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40">
+        <v>42406507</v>
+      </c>
+      <c r="L40">
+        <v>3754003</v>
+      </c>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>42406507</v>
+      </c>
+      <c r="B41">
         <v>4239307</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="K41">
+        <v>42406507</v>
+      </c>
+      <c r="L41">
+        <v>4239307</v>
+      </c>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>42406507</v>
+      </c>
+      <c r="B42">
         <v>31956677</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42">
+        <v>42406507</v>
+      </c>
+      <c r="L42">
+        <v>31956677</v>
+      </c>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42406507</v>
+      </c>
+      <c r="B43">
         <v>42010347</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43">
+        <v>42406507</v>
+      </c>
+      <c r="L43">
+        <v>42010347</v>
+      </c>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>42406507</v>
+      </c>
+      <c r="B44">
         <v>42012522</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44">
+        <v>42406507</v>
+      </c>
+      <c r="L44">
+        <v>42012522</v>
+      </c>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>42406507</v>
+      </c>
+      <c r="B45">
         <v>42079879</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K45">
+        <v>42406507</v>
+      </c>
+      <c r="L45">
+        <v>42079879</v>
+      </c>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>42406507</v>
+      </c>
+      <c r="B46">
         <v>42814075</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+      <c r="K46">
+        <v>42406507</v>
+      </c>
+      <c r="L46">
+        <v>42814075</v>
+      </c>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>42406507</v>
+      </c>
+      <c r="B47">
         <v>43110281</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47">
+        <v>42406507</v>
+      </c>
+      <c r="L47">
+        <v>43110281</v>
+      </c>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>42458992</v>
+      </c>
+      <c r="B48">
         <v>42459041</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="K48">
+        <v>42458992</v>
+      </c>
+      <c r="L48">
+        <v>42459041</v>
+      </c>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>42463024</v>
+      </c>
+      <c r="B49">
         <v>42463063</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="K49">
         <v>42463024</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>10</v>
+      <c r="L49">
+        <v>42463063</v>
+      </c>
+      <c r="M49" s="2"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>42463063</v>
+      </c>
+      <c r="B50">
+        <v>42463024</v>
       </c>
       <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="K50">
+        <v>42463063</v>
+      </c>
+      <c r="L50">
+        <v>42463024</v>
+      </c>
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>42705635</v>
+      </c>
+      <c r="B51">
         <v>42731028</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="K51">
+        <v>42705635</v>
+      </c>
+      <c r="L51">
+        <v>42731028</v>
+      </c>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>43593087</v>
+      </c>
+      <c r="B52">
         <v>43613297</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C52" t="s">
-        <v>13</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="K52">
+        <v>43593087</v>
+      </c>
+      <c r="L52">
+        <v>43613297</v>
+      </c>
+      <c r="M52" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C52" xr:uid="{25ED12FD-7613-4161-AB77-60A5E5F0FD4C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>